--- a/Archivos de cursos/Listado_Grupo_pagos.xlsx
+++ b/Archivos de cursos/Listado_Grupo_pagos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAUL\Desktop\Raúl Mena\Programación\Proyecto 4 (PaginaWeb)\Archivos de cursos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A85C936E-6FE6-43EC-B78F-F3A583BC29C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E06C4265-CE1F-47BA-AF91-071681736A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,11 @@
     <sheet name="Listado del Grupo" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="37">
   <si>
     <t>📋  LISTADO DEL GRUPO</t>
   </si>
@@ -123,9 +122,6 @@
   </si>
   <si>
     <t xml:space="preserve">Julio Chacón </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Falta pagar 100 soles, pagó 50 </t>
   </si>
   <si>
     <t xml:space="preserve">Harry de Lama Rodríguez </t>
@@ -902,11 +898,11 @@
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>26</v>
@@ -1002,17 +998,19 @@
         <v>10</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
+      <c r="F14" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="G14" s="7"/>
       <c r="H14" s="6" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I14" s="7"/>
     </row>
@@ -1021,7 +1019,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="4"/>
@@ -1036,7 +1034,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C16" s="6">
         <v>51941930388</v>
